--- a/data/3420-2025-fall-quizzes/quizzes-student-work-data.xlsx
+++ b/data/3420-2025-fall-quizzes/quizzes-student-work-data.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tcn85/workspace/dsm/data/3420-2025-fall-quizzes/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{822D56A6-AAA0-F741-838D-D09769EEC04B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40C25B3B-70F4-3E41-9B75-9DDEBD3221DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-32100" yWindow="-1340" windowWidth="32100" windowHeight="20980" activeTab="2" xr2:uid="{02943BD8-8D23-1D42-A928-8937731C9A90}"/>
+    <workbookView xWindow="-20660" yWindow="-1340" windowWidth="20660" windowHeight="20980" xr2:uid="{02943BD8-8D23-1D42-A928-8937731C9A90}"/>
   </bookViews>
   <sheets>
-    <sheet name="py-np-pd-2" sheetId="4" r:id="rId1"/>
-    <sheet name="py-np-pd" sheetId="3" r:id="rId2"/>
-    <sheet name="py-review" sheetId="2" r:id="rId3"/>
+    <sheet name="midterm" sheetId="5" r:id="rId1"/>
+    <sheet name="py-np-pd-2" sheetId="4" r:id="rId2"/>
+    <sheet name="py-np-pd" sheetId="3" r:id="rId3"/>
+    <sheet name="py-review" sheetId="2" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="26">
   <si>
     <t>total</t>
   </si>
@@ -497,6 +498,217 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37348E0A-6C4B-7145-865E-B4DD903EA285}">
+  <dimension ref="A2:M24"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="7.33203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="7.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="3.5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>19</v>
+      </c>
+      <c r="B3">
+        <v>50</v>
+      </c>
+      <c r="M3" s="2"/>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>7</v>
+      </c>
+      <c r="B4">
+        <v>50</v>
+      </c>
+      <c r="M4" s="2"/>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5">
+        <v>46</v>
+      </c>
+      <c r="M5" s="2"/>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>12</v>
+      </c>
+      <c r="B6">
+        <v>50</v>
+      </c>
+      <c r="M6" s="2"/>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>18</v>
+      </c>
+      <c r="B7">
+        <v>50</v>
+      </c>
+      <c r="M7" s="2"/>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>2</v>
+      </c>
+      <c r="B8">
+        <v>48</v>
+      </c>
+      <c r="M8" s="2"/>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>15</v>
+      </c>
+      <c r="B9">
+        <v>45</v>
+      </c>
+      <c r="M9" s="2"/>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>6</v>
+      </c>
+      <c r="B10">
+        <v>48</v>
+      </c>
+      <c r="M10" s="2"/>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>16</v>
+      </c>
+      <c r="B11">
+        <v>50</v>
+      </c>
+      <c r="M11" s="2"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <v>14</v>
+      </c>
+      <c r="B12">
+        <v>47</v>
+      </c>
+      <c r="M12" s="2"/>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>13</v>
+      </c>
+      <c r="B13">
+        <v>50</v>
+      </c>
+      <c r="M13" s="2"/>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A14">
+        <v>20</v>
+      </c>
+      <c r="B14" t="s">
+        <v>22</v>
+      </c>
+      <c r="M14" s="2"/>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A15">
+        <v>17</v>
+      </c>
+      <c r="B15">
+        <v>48</v>
+      </c>
+      <c r="M15" s="2"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A16">
+        <v>11</v>
+      </c>
+      <c r="B16">
+        <v>46</v>
+      </c>
+      <c r="M16" s="2"/>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A17">
+        <v>5</v>
+      </c>
+      <c r="B17">
+        <v>38</v>
+      </c>
+      <c r="M17" s="2"/>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A18">
+        <v>1</v>
+      </c>
+      <c r="B18">
+        <v>48</v>
+      </c>
+      <c r="M18" s="2"/>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A19">
+        <v>9</v>
+      </c>
+      <c r="B19">
+        <v>45</v>
+      </c>
+      <c r="M19" s="2"/>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A20">
+        <v>10</v>
+      </c>
+      <c r="B20">
+        <v>48</v>
+      </c>
+      <c r="M20" s="2"/>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A21">
+        <v>8</v>
+      </c>
+      <c r="B21">
+        <v>48</v>
+      </c>
+      <c r="M21" s="2"/>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A22">
+        <v>4</v>
+      </c>
+      <c r="B22">
+        <v>50</v>
+      </c>
+      <c r="M22" s="2"/>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="B24" s="1"/>
+      <c r="C24" s="1"/>
+      <c r="D24" s="1"/>
+      <c r="E24" s="1"/>
+      <c r="F24" s="1"/>
+      <c r="G24" s="1"/>
+      <c r="H24" s="1"/>
+      <c r="I24" s="1"/>
+      <c r="J24" s="1"/>
+      <c r="K24" s="1"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BACDFB91-6B06-BF4E-90E6-DEB9ED31E513}">
   <dimension ref="A2:H24"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="3.33203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -1156,7 +1368,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{625988FA-08F2-5D4B-BCDA-BABB71AA94B0}">
   <dimension ref="A2:I24"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.1640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -1875,7 +2087,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C470603-E249-6C49-AFDF-564C1138E589}">
   <dimension ref="A1:M24"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="3.33203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
